--- a/artfynd/A 5140-2024 artfynd.xlsx
+++ b/artfynd/A 5140-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY208"/>
+  <dimension ref="A1:AY209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487924</v>
+        <v>120487764</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>90600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436247</v>
+        <v>436525</v>
       </c>
       <c r="R2" t="n">
-        <v>6757593</v>
+        <v>6757786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487764</v>
+        <v>120487782</v>
       </c>
       <c r="B3" t="n">
-        <v>90600</v>
+        <v>90864</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +793,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436525</v>
+        <v>436408</v>
       </c>
       <c r="R3" t="n">
-        <v>6757786</v>
+        <v>6757458</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487782</v>
+        <v>120487899</v>
       </c>
       <c r="B4" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,43 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436408</v>
+        <v>436407</v>
       </c>
       <c r="R4" t="n">
-        <v>6757458</v>
+        <v>6757442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487899</v>
+        <v>120487822</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1039,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436407</v>
+        <v>436517</v>
       </c>
       <c r="R5" t="n">
-        <v>6757442</v>
+        <v>6757429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487822</v>
+        <v>120487942</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436517</v>
+        <v>436512</v>
       </c>
       <c r="R6" t="n">
-        <v>6757429</v>
+        <v>6757714</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487942</v>
+        <v>120487788</v>
       </c>
       <c r="B7" t="n">
-        <v>78187</v>
+        <v>8432</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,38 +1206,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436512</v>
+        <v>436509</v>
       </c>
       <c r="R7" t="n">
-        <v>6757714</v>
+        <v>6757743</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487788</v>
+        <v>120487766</v>
       </c>
       <c r="B8" t="n">
-        <v>8432</v>
+        <v>90600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,43 +1313,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436509</v>
+        <v>436466</v>
       </c>
       <c r="R8" t="n">
-        <v>6757743</v>
+        <v>6757755</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487766</v>
+        <v>120487821</v>
       </c>
       <c r="B9" t="n">
-        <v>90600</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436466</v>
+        <v>436511</v>
       </c>
       <c r="R9" t="n">
-        <v>6757755</v>
+        <v>6757442</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1505,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487821</v>
+        <v>120487843</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1554,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436511</v>
+        <v>436507</v>
       </c>
       <c r="R10" t="n">
-        <v>6757442</v>
+        <v>6757735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1607,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487843</v>
+        <v>120487873</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1656,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436507</v>
+        <v>436338</v>
       </c>
       <c r="R11" t="n">
-        <v>6757735</v>
+        <v>6757450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487873</v>
+        <v>120487924</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,38 +1721,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436338</v>
+        <v>436247</v>
       </c>
       <c r="R12" t="n">
-        <v>6757450</v>
+        <v>6757593</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487757</v>
+        <v>120487817</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>89981</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,42 +2351,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436404</v>
+        <v>436347</v>
       </c>
       <c r="R18" t="n">
-        <v>6757479</v>
+        <v>6757700</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,10 +2441,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487704</v>
+        <v>120487895</v>
       </c>
       <c r="B19" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,21 +2457,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2485,10 +2481,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436459</v>
+        <v>436399</v>
       </c>
       <c r="R19" t="n">
-        <v>6757737</v>
+        <v>6757445</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2547,10 +2543,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487817</v>
+        <v>120487793</v>
       </c>
       <c r="B20" t="n">
-        <v>89981</v>
+        <v>8432</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,34 +2559,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5685</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436347</v>
+        <v>436588</v>
       </c>
       <c r="R20" t="n">
-        <v>6757700</v>
+        <v>6757466</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2649,7 +2650,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487895</v>
+        <v>120487869</v>
       </c>
       <c r="B21" t="n">
         <v>78542</v>
@@ -2689,10 +2690,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436399</v>
+        <v>436330</v>
       </c>
       <c r="R21" t="n">
-        <v>6757445</v>
+        <v>6757450</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2751,10 +2752,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487793</v>
+        <v>120487866</v>
       </c>
       <c r="B22" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2763,43 +2764,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436588</v>
+        <v>436271</v>
       </c>
       <c r="R22" t="n">
-        <v>6757466</v>
+        <v>6757617</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2858,7 +2854,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120487869</v>
+        <v>120487839</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -2898,10 +2894,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436330</v>
+        <v>436548</v>
       </c>
       <c r="R23" t="n">
-        <v>6757450</v>
+        <v>6757697</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2960,7 +2956,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120487866</v>
+        <v>120487851</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -3000,10 +2996,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436271</v>
+        <v>436460</v>
       </c>
       <c r="R24" t="n">
-        <v>6757617</v>
+        <v>6757758</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3062,10 +3058,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120487839</v>
+        <v>120487757</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3078,34 +3074,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436548</v>
+        <v>436404</v>
       </c>
       <c r="R25" t="n">
-        <v>6757697</v>
+        <v>6757479</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120487851</v>
+        <v>120487704</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3180,21 +3180,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436460</v>
+        <v>436459</v>
       </c>
       <c r="R26" t="n">
-        <v>6757758</v>
+        <v>6757737</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4815,10 +4815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120487719</v>
+        <v>120487887</v>
       </c>
       <c r="B42" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4827,25 +4827,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436572</v>
+        <v>436404</v>
       </c>
       <c r="R42" t="n">
-        <v>6757654</v>
+        <v>6757477</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4917,10 +4917,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120487887</v>
+        <v>120487968</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4933,21 +4933,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436404</v>
+        <v>436264</v>
       </c>
       <c r="R43" t="n">
-        <v>6757477</v>
+        <v>6757686</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120487968</v>
+        <v>120487850</v>
       </c>
       <c r="B44" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5035,21 +5035,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436264</v>
+        <v>436471</v>
       </c>
       <c r="R44" t="n">
-        <v>6757686</v>
+        <v>6757754</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5121,10 +5121,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120487850</v>
+        <v>120487933</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5137,21 +5137,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436471</v>
+        <v>436528</v>
       </c>
       <c r="R45" t="n">
-        <v>6757754</v>
+        <v>6757704</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5223,10 +5223,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120487933</v>
+        <v>120487719</v>
       </c>
       <c r="B46" t="n">
-        <v>78187</v>
+        <v>90545</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5235,25 +5235,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436528</v>
+        <v>436572</v>
       </c>
       <c r="R46" t="n">
-        <v>6757704</v>
+        <v>6757654</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120487882</v>
+        <v>120487731</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>79131</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5341,21 +5341,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436381</v>
+        <v>436249</v>
       </c>
       <c r="R47" t="n">
-        <v>6757466</v>
+        <v>6757689</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5427,10 +5427,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120487848</v>
+        <v>120487742</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5443,34 +5443,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436484</v>
+        <v>436384</v>
       </c>
       <c r="R48" t="n">
-        <v>6757836</v>
+        <v>6757467</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5529,10 +5538,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120487972</v>
+        <v>120487685</v>
       </c>
       <c r="B49" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5545,21 +5554,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5578,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436289</v>
+        <v>436264</v>
       </c>
       <c r="R49" t="n">
-        <v>6757610</v>
+        <v>6757686</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,10 +5640,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120487854</v>
+        <v>120487694</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5647,21 +5656,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5671,10 +5680,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436460</v>
+        <v>436278</v>
       </c>
       <c r="R50" t="n">
-        <v>6757739</v>
+        <v>6757591</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5733,10 +5742,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120487878</v>
+        <v>120487687</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5749,21 +5758,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5773,10 +5782,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436369</v>
+        <v>436309</v>
       </c>
       <c r="R51" t="n">
-        <v>6757462</v>
+        <v>6757626</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5835,7 +5844,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120487840</v>
+        <v>120487882</v>
       </c>
       <c r="B52" t="n">
         <v>78542</v>
@@ -5875,10 +5884,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436543</v>
+        <v>436381</v>
       </c>
       <c r="R52" t="n">
-        <v>6757720</v>
+        <v>6757466</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5937,10 +5946,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120487979</v>
+        <v>120487848</v>
       </c>
       <c r="B53" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5953,21 +5962,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5977,10 +5986,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436297</v>
+        <v>436484</v>
       </c>
       <c r="R53" t="n">
-        <v>6757476</v>
+        <v>6757836</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6141,10 +6150,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120487894</v>
+        <v>120487972</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6157,21 +6166,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6181,10 +6190,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436416</v>
+        <v>436289</v>
       </c>
       <c r="R55" t="n">
-        <v>6757462</v>
+        <v>6757610</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,10 +6252,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120487731</v>
+        <v>120487854</v>
       </c>
       <c r="B56" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6259,21 +6268,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6283,10 +6292,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436249</v>
+        <v>436460</v>
       </c>
       <c r="R56" t="n">
-        <v>6757689</v>
+        <v>6757739</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6345,10 +6354,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120487742</v>
+        <v>120487878</v>
       </c>
       <c r="B57" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6361,43 +6370,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436384</v>
+        <v>436369</v>
       </c>
       <c r="R57" t="n">
-        <v>6757467</v>
+        <v>6757462</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6456,10 +6456,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120487685</v>
+        <v>120487840</v>
       </c>
       <c r="B58" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6472,21 +6472,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436264</v>
+        <v>436543</v>
       </c>
       <c r="R58" t="n">
-        <v>6757686</v>
+        <v>6757720</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6558,10 +6558,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120487694</v>
+        <v>120487894</v>
       </c>
       <c r="B59" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6574,21 +6574,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6598,10 +6598,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>436278</v>
+        <v>436416</v>
       </c>
       <c r="R59" t="n">
-        <v>6757591</v>
+        <v>6757462</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6660,10 +6660,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120487687</v>
+        <v>120487979</v>
       </c>
       <c r="B60" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6676,21 +6676,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6700,10 +6700,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>436309</v>
+        <v>436297</v>
       </c>
       <c r="R60" t="n">
-        <v>6757626</v>
+        <v>6757476</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120487961</v>
+        <v>120487706</v>
       </c>
       <c r="B79" t="n">
-        <v>78187</v>
+        <v>74654</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8656,21 +8656,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436390</v>
+        <v>436410</v>
       </c>
       <c r="R79" t="n">
-        <v>6757715</v>
+        <v>6757457</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8742,10 +8742,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120487802</v>
+        <v>120487749</v>
       </c>
       <c r="B80" t="n">
-        <v>8432</v>
+        <v>90580</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8754,31 +8754,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8787,10 +8791,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436410</v>
+        <v>436412</v>
       </c>
       <c r="R80" t="n">
-        <v>6757695</v>
+        <v>6757460</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8849,10 +8853,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120487846</v>
+        <v>120487683</v>
       </c>
       <c r="B81" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8865,21 +8869,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8889,10 +8893,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436510</v>
+        <v>436358</v>
       </c>
       <c r="R81" t="n">
-        <v>6757784</v>
+        <v>6757681</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8951,7 +8955,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120487936</v>
+        <v>120487961</v>
       </c>
       <c r="B82" t="n">
         <v>78187</v>
@@ -8991,10 +8995,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436543</v>
+        <v>436390</v>
       </c>
       <c r="R82" t="n">
-        <v>6757716</v>
+        <v>6757715</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9053,10 +9057,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120487948</v>
+        <v>120487802</v>
       </c>
       <c r="B83" t="n">
-        <v>78187</v>
+        <v>8432</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9065,38 +9069,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436432</v>
+        <v>436410</v>
       </c>
       <c r="R83" t="n">
-        <v>6757715</v>
+        <v>6757695</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9155,10 +9164,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120487808</v>
+        <v>120487936</v>
       </c>
       <c r="B84" t="n">
-        <v>8432</v>
+        <v>78187</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9167,43 +9176,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>436494</v>
+        <v>436543</v>
       </c>
       <c r="R84" t="n">
-        <v>6757416</v>
+        <v>6757716</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9364,10 +9368,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120487706</v>
+        <v>120487846</v>
       </c>
       <c r="B86" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9380,21 +9384,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9404,10 +9408,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436410</v>
+        <v>436510</v>
       </c>
       <c r="R86" t="n">
-        <v>6757457</v>
+        <v>6757784</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9466,10 +9470,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120487749</v>
+        <v>120487948</v>
       </c>
       <c r="B87" t="n">
-        <v>90580</v>
+        <v>78187</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9482,43 +9486,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436412</v>
+        <v>436432</v>
       </c>
       <c r="R87" t="n">
-        <v>6757460</v>
+        <v>6757715</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9577,10 +9572,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120487683</v>
+        <v>120487808</v>
       </c>
       <c r="B88" t="n">
-        <v>79160</v>
+        <v>8432</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9589,38 +9584,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436358</v>
+        <v>436494</v>
       </c>
       <c r="R88" t="n">
-        <v>6757681</v>
+        <v>6757416</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9679,10 +9679,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120487661</v>
+        <v>120487834</v>
       </c>
       <c r="B89" t="n">
-        <v>5189</v>
+        <v>78542</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9691,43 +9691,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436437</v>
+        <v>436594</v>
       </c>
       <c r="R89" t="n">
-        <v>6757717</v>
+        <v>6757688</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9786,10 +9781,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120487737</v>
+        <v>120487965</v>
       </c>
       <c r="B90" t="n">
-        <v>90580</v>
+        <v>78187</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9802,43 +9797,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436588</v>
+        <v>436382</v>
       </c>
       <c r="R90" t="n">
-        <v>6757482</v>
+        <v>6757729</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9897,10 +9883,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120487709</v>
+        <v>120487987</v>
       </c>
       <c r="B91" t="n">
-        <v>78576</v>
+        <v>5169</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9909,38 +9895,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436480</v>
+        <v>436416</v>
       </c>
       <c r="R91" t="n">
-        <v>6757418</v>
+        <v>6757447</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9999,7 +9990,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120487834</v>
+        <v>120487870</v>
       </c>
       <c r="B92" t="n">
         <v>78542</v>
@@ -10039,10 +10030,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436594</v>
+        <v>436330</v>
       </c>
       <c r="R92" t="n">
-        <v>6757688</v>
+        <v>6757457</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10101,10 +10092,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120487965</v>
+        <v>120487661</v>
       </c>
       <c r="B93" t="n">
-        <v>78187</v>
+        <v>5189</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10113,38 +10104,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>105930</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436382</v>
+        <v>436437</v>
       </c>
       <c r="R93" t="n">
-        <v>6757729</v>
+        <v>6757717</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10203,10 +10199,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120487987</v>
+        <v>120487737</v>
       </c>
       <c r="B94" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10215,31 +10211,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10248,10 +10248,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436416</v>
+        <v>436588</v>
       </c>
       <c r="R94" t="n">
-        <v>6757447</v>
+        <v>6757482</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10310,10 +10310,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120487870</v>
+        <v>120487709</v>
       </c>
       <c r="B95" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10326,21 +10326,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10350,10 +10350,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436330</v>
+        <v>436480</v>
       </c>
       <c r="R95" t="n">
-        <v>6757457</v>
+        <v>6757418</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11330,7 +11330,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120487835</v>
+        <v>120487886</v>
       </c>
       <c r="B105" t="n">
         <v>78542</v>
@@ -11370,10 +11370,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436584</v>
+        <v>436399</v>
       </c>
       <c r="R105" t="n">
-        <v>6757687</v>
+        <v>6757467</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11432,10 +11432,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120487777</v>
+        <v>120487837</v>
       </c>
       <c r="B106" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11448,43 +11448,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436563</v>
+        <v>436570</v>
       </c>
       <c r="R106" t="n">
-        <v>6757614</v>
+        <v>6757696</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11543,7 +11534,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120487886</v>
+        <v>120487879</v>
       </c>
       <c r="B107" t="n">
         <v>78542</v>
@@ -11583,10 +11574,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436399</v>
+        <v>436367</v>
       </c>
       <c r="R107" t="n">
-        <v>6757467</v>
+        <v>6757474</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11645,7 +11636,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120487837</v>
+        <v>120487865</v>
       </c>
       <c r="B108" t="n">
         <v>78542</v>
@@ -11685,10 +11676,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436570</v>
+        <v>436296</v>
       </c>
       <c r="R108" t="n">
-        <v>6757696</v>
+        <v>6757624</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11747,7 +11738,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120487879</v>
+        <v>120487835</v>
       </c>
       <c r="B109" t="n">
         <v>78542</v>
@@ -11787,10 +11778,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436367</v>
+        <v>436584</v>
       </c>
       <c r="R109" t="n">
-        <v>6757474</v>
+        <v>6757687</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11849,10 +11840,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120487865</v>
+        <v>120487777</v>
       </c>
       <c r="B110" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11865,34 +11856,43 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>436296</v>
+        <v>436563</v>
       </c>
       <c r="R110" t="n">
-        <v>6757624</v>
+        <v>6757614</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -16113,10 +16113,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120487781</v>
+        <v>120487682</v>
       </c>
       <c r="B151" t="n">
-        <v>90864</v>
+        <v>79160</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16129,43 +16129,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436425</v>
+        <v>436354</v>
       </c>
       <c r="R151" t="n">
-        <v>6757468</v>
+        <v>6757705</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16224,10 +16215,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120487842</v>
+        <v>120487681</v>
       </c>
       <c r="B152" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16240,21 +16231,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16264,10 +16255,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436530</v>
+        <v>436366</v>
       </c>
       <c r="R152" t="n">
-        <v>6757717</v>
+        <v>6757705</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16326,10 +16317,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120487952</v>
+        <v>120487781</v>
       </c>
       <c r="B153" t="n">
-        <v>78187</v>
+        <v>90864</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16342,34 +16333,43 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>436423</v>
+        <v>436425</v>
       </c>
       <c r="R153" t="n">
-        <v>6757707</v>
+        <v>6757468</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16428,10 +16428,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120487811</v>
+        <v>120487842</v>
       </c>
       <c r="B154" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16440,47 +16440,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>436540</v>
+        <v>436530</v>
       </c>
       <c r="R154" t="n">
-        <v>6757601</v>
+        <v>6757717</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16539,10 +16530,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120487880</v>
+        <v>120487952</v>
       </c>
       <c r="B155" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16555,21 +16546,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16579,10 +16570,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>436389</v>
+        <v>436423</v>
       </c>
       <c r="R155" t="n">
-        <v>6757480</v>
+        <v>6757707</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16641,10 +16632,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120487780</v>
+        <v>120487811</v>
       </c>
       <c r="B156" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16653,35 +16644,35 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -16690,10 +16681,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>436441</v>
+        <v>436540</v>
       </c>
       <c r="R156" t="n">
-        <v>6757466</v>
+        <v>6757601</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16752,7 +16743,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120487820</v>
+        <v>120487880</v>
       </c>
       <c r="B157" t="n">
         <v>78542</v>
@@ -16792,10 +16783,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>436458</v>
+        <v>436389</v>
       </c>
       <c r="R157" t="n">
-        <v>6757464</v>
+        <v>6757480</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16854,10 +16845,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120487864</v>
+        <v>120487780</v>
       </c>
       <c r="B158" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16870,34 +16861,43 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>436293</v>
+        <v>436441</v>
       </c>
       <c r="R158" t="n">
-        <v>6757634</v>
+        <v>6757466</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16956,10 +16956,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120487682</v>
+        <v>120487820</v>
       </c>
       <c r="B159" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16972,21 +16972,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16996,10 +16996,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>436354</v>
+        <v>436458</v>
       </c>
       <c r="R159" t="n">
-        <v>6757705</v>
+        <v>6757464</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17058,10 +17058,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120487681</v>
+        <v>120487864</v>
       </c>
       <c r="B160" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17074,21 +17074,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17098,10 +17098,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>436366</v>
+        <v>436293</v>
       </c>
       <c r="R160" t="n">
-        <v>6757705</v>
+        <v>6757634</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -22100,6 +22100,121 @@
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>120487755</v>
+      </c>
+      <c r="B209" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Hagmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>436460</v>
+      </c>
+      <c r="R209" t="n">
+        <v>6757758</v>
+      </c>
+      <c r="S209" t="n">
+        <v>10</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>2 st bohål i rätt storlek och på rätt höjd i tall</t>
+        </is>
+      </c>
+      <c r="AD209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5140-2024 artfynd.xlsx
+++ b/artfynd/A 5140-2024 artfynd.xlsx
@@ -5014,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120487685</v>
+        <v>120487776</v>
       </c>
       <c r="B44" t="n">
-        <v>79160</v>
+        <v>91023</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5026,38 +5026,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436264</v>
+        <v>436407</v>
       </c>
       <c r="R44" t="n">
-        <v>6757686</v>
+        <v>6757458</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,10 +5125,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120487722</v>
+        <v>120487685</v>
       </c>
       <c r="B45" t="n">
-        <v>90545</v>
+        <v>79160</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5128,25 +5137,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5156,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436302</v>
+        <v>436264</v>
       </c>
       <c r="R45" t="n">
-        <v>6757638</v>
+        <v>6757686</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5227,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120487843</v>
+        <v>120487722</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5230,25 +5239,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5258,10 +5267,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436507</v>
+        <v>436302</v>
       </c>
       <c r="R46" t="n">
-        <v>6757735</v>
+        <v>6757638</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,7 +5329,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120487896</v>
+        <v>120487843</v>
       </c>
       <c r="B47" t="n">
         <v>78542</v>
@@ -5360,10 +5369,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436389</v>
+        <v>436507</v>
       </c>
       <c r="R47" t="n">
-        <v>6757440</v>
+        <v>6757735</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5422,7 +5431,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120487876</v>
+        <v>120487896</v>
       </c>
       <c r="B48" t="n">
         <v>78542</v>
@@ -5462,10 +5471,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436370</v>
+        <v>436389</v>
       </c>
       <c r="R48" t="n">
-        <v>6757441</v>
+        <v>6757440</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,7 +5533,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120487903</v>
+        <v>120487876</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -5564,10 +5573,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436470</v>
+        <v>436370</v>
       </c>
       <c r="R49" t="n">
-        <v>6757435</v>
+        <v>6757441</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5626,7 +5635,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120487854</v>
+        <v>120487903</v>
       </c>
       <c r="B50" t="n">
         <v>78542</v>
@@ -5666,10 +5675,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436460</v>
+        <v>436470</v>
       </c>
       <c r="R50" t="n">
-        <v>6757739</v>
+        <v>6757435</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,7 +5737,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120487851</v>
+        <v>120487854</v>
       </c>
       <c r="B51" t="n">
         <v>78542</v>
@@ -5771,7 +5780,7 @@
         <v>436460</v>
       </c>
       <c r="R51" t="n">
-        <v>6757758</v>
+        <v>6757739</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,10 +5839,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120487729</v>
+        <v>120487851</v>
       </c>
       <c r="B52" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5846,21 +5855,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5870,10 +5879,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436512</v>
+        <v>436460</v>
       </c>
       <c r="R52" t="n">
-        <v>6757751</v>
+        <v>6757758</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,10 +5941,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120487780</v>
+        <v>120487729</v>
       </c>
       <c r="B53" t="n">
-        <v>90864</v>
+        <v>79131</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5948,43 +5957,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436441</v>
+        <v>436512</v>
       </c>
       <c r="R53" t="n">
-        <v>6757466</v>
+        <v>6757751</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120487776</v>
+        <v>120487780</v>
       </c>
       <c r="B55" t="n">
-        <v>91023</v>
+        <v>90864</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6157,25 +6157,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436407</v>
+        <v>436441</v>
       </c>
       <c r="R55" t="n">
-        <v>6757458</v>
+        <v>6757466</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7396,10 +7396,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120487790</v>
+        <v>120487971</v>
       </c>
       <c r="B67" t="n">
-        <v>8432</v>
+        <v>78187</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7408,43 +7408,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436579</v>
+        <v>436292</v>
       </c>
       <c r="R67" t="n">
-        <v>6757471</v>
+        <v>6757604</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7503,10 +7498,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120487675</v>
+        <v>120487924</v>
       </c>
       <c r="B68" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7515,38 +7510,47 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436511</v>
+        <v>436247</v>
       </c>
       <c r="R68" t="n">
-        <v>6757783</v>
+        <v>6757593</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7605,10 +7609,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120487719</v>
+        <v>120487675</v>
       </c>
       <c r="B69" t="n">
-        <v>90545</v>
+        <v>79160</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7617,25 +7621,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7645,10 +7649,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436572</v>
+        <v>436511</v>
       </c>
       <c r="R69" t="n">
-        <v>6757654</v>
+        <v>6757783</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7707,10 +7711,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120487971</v>
+        <v>120487719</v>
       </c>
       <c r="B70" t="n">
-        <v>78187</v>
+        <v>90545</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7719,25 +7723,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7747,10 +7751,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436292</v>
+        <v>436572</v>
       </c>
       <c r="R70" t="n">
-        <v>6757604</v>
+        <v>6757654</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7809,10 +7813,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120487924</v>
+        <v>120487869</v>
       </c>
       <c r="B71" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7821,47 +7825,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436247</v>
+        <v>436330</v>
       </c>
       <c r="R71" t="n">
-        <v>6757593</v>
+        <v>6757450</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7920,7 +7915,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120487869</v>
+        <v>120487874</v>
       </c>
       <c r="B72" t="n">
         <v>78542</v>
@@ -7960,10 +7955,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436330</v>
+        <v>436354</v>
       </c>
       <c r="R72" t="n">
-        <v>6757450</v>
+        <v>6757441</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8022,10 +8017,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120487874</v>
+        <v>120487790</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
+        <v>8432</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8034,38 +8029,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436354</v>
+        <v>436579</v>
       </c>
       <c r="R73" t="n">
-        <v>6757441</v>
+        <v>6757471</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9376,10 +9376,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120487775</v>
+        <v>120487684</v>
       </c>
       <c r="B86" t="n">
-        <v>91023</v>
+        <v>79160</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9388,47 +9388,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436425</v>
+        <v>436309</v>
       </c>
       <c r="R86" t="n">
-        <v>6757469</v>
+        <v>6757685</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9487,10 +9478,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120487684</v>
+        <v>120487990</v>
       </c>
       <c r="B87" t="n">
-        <v>79160</v>
+        <v>77474</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9503,21 +9494,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9527,10 +9518,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436309</v>
+        <v>436244</v>
       </c>
       <c r="R87" t="n">
-        <v>6757685</v>
+        <v>6757596</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9589,10 +9580,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120487990</v>
+        <v>120487761</v>
       </c>
       <c r="B88" t="n">
-        <v>77474</v>
+        <v>90600</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9605,21 +9596,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6487</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9629,10 +9620,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436244</v>
+        <v>436586</v>
       </c>
       <c r="R88" t="n">
-        <v>6757596</v>
+        <v>6757467</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9691,10 +9682,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120487761</v>
+        <v>120487811</v>
       </c>
       <c r="B89" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9703,38 +9694,47 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436586</v>
+        <v>436540</v>
       </c>
       <c r="R89" t="n">
-        <v>6757467</v>
+        <v>6757601</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9793,10 +9793,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120487881</v>
+        <v>120487775</v>
       </c>
       <c r="B90" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9805,38 +9805,47 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436388</v>
+        <v>436425</v>
       </c>
       <c r="R90" t="n">
-        <v>6757470</v>
+        <v>6757469</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9895,10 +9904,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120487705</v>
+        <v>120487881</v>
       </c>
       <c r="B91" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9911,21 +9920,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9935,10 +9944,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436415</v>
+        <v>436388</v>
       </c>
       <c r="R91" t="n">
-        <v>6757463</v>
+        <v>6757470</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9997,10 +10006,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120487908</v>
+        <v>120487705</v>
       </c>
       <c r="B92" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10013,21 +10022,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10037,10 +10046,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436498</v>
+        <v>436415</v>
       </c>
       <c r="R92" t="n">
-        <v>6757403</v>
+        <v>6757463</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10099,7 +10108,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120487899</v>
+        <v>120487908</v>
       </c>
       <c r="B93" t="n">
         <v>78542</v>
@@ -10139,10 +10148,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436407</v>
+        <v>436498</v>
       </c>
       <c r="R93" t="n">
-        <v>6757442</v>
+        <v>6757403</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10201,7 +10210,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120487879</v>
+        <v>120487899</v>
       </c>
       <c r="B94" t="n">
         <v>78542</v>
@@ -10241,10 +10250,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436367</v>
+        <v>436407</v>
       </c>
       <c r="R94" t="n">
-        <v>6757474</v>
+        <v>6757442</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10303,7 +10312,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120487882</v>
+        <v>120487879</v>
       </c>
       <c r="B95" t="n">
         <v>78542</v>
@@ -10343,10 +10352,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436381</v>
+        <v>436367</v>
       </c>
       <c r="R95" t="n">
-        <v>6757466</v>
+        <v>6757474</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10405,7 +10414,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120487845</v>
+        <v>120487882</v>
       </c>
       <c r="B96" t="n">
         <v>78542</v>
@@ -10445,10 +10454,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436513</v>
+        <v>436381</v>
       </c>
       <c r="R96" t="n">
-        <v>6757781</v>
+        <v>6757466</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,7 +10516,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120487901</v>
+        <v>120487845</v>
       </c>
       <c r="B97" t="n">
         <v>78542</v>
@@ -10547,10 +10556,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436459</v>
+        <v>436513</v>
       </c>
       <c r="R97" t="n">
-        <v>6757422</v>
+        <v>6757781</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10609,10 +10618,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120487811</v>
+        <v>120487901</v>
       </c>
       <c r="B98" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10621,47 +10630,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436540</v>
+        <v>436459</v>
       </c>
       <c r="R98" t="n">
-        <v>6757601</v>
+        <v>6757422</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12912,10 +12912,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120487985</v>
+        <v>120487965</v>
       </c>
       <c r="B120" t="n">
-        <v>5169</v>
+        <v>78187</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12924,43 +12924,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100526</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436401</v>
+        <v>436382</v>
       </c>
       <c r="R120" t="n">
-        <v>6757463</v>
+        <v>6757729</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13019,10 +13014,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120487965</v>
+        <v>120487707</v>
       </c>
       <c r="B121" t="n">
-        <v>78187</v>
+        <v>78576</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13035,21 +13030,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13059,10 +13054,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436382</v>
+        <v>436387</v>
       </c>
       <c r="R121" t="n">
-        <v>6757729</v>
+        <v>6757443</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13121,10 +13116,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120487707</v>
+        <v>120487741</v>
       </c>
       <c r="B122" t="n">
-        <v>78576</v>
+        <v>90580</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13137,34 +13132,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436387</v>
+        <v>436397</v>
       </c>
       <c r="R122" t="n">
-        <v>6757443</v>
+        <v>6757474</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13223,10 +13227,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120487741</v>
+        <v>120487681</v>
       </c>
       <c r="B123" t="n">
-        <v>90580</v>
+        <v>79160</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13239,43 +13243,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436397</v>
+        <v>436366</v>
       </c>
       <c r="R123" t="n">
-        <v>6757474</v>
+        <v>6757705</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13334,10 +13329,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120487681</v>
+        <v>120487766</v>
       </c>
       <c r="B124" t="n">
-        <v>79160</v>
+        <v>90600</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13350,21 +13345,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13374,10 +13369,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436366</v>
+        <v>436466</v>
       </c>
       <c r="R124" t="n">
-        <v>6757705</v>
+        <v>6757755</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13436,10 +13431,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120487766</v>
+        <v>120487900</v>
       </c>
       <c r="B125" t="n">
-        <v>90600</v>
+        <v>78542</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13452,21 +13447,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13476,10 +13471,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436466</v>
+        <v>436417</v>
       </c>
       <c r="R125" t="n">
-        <v>6757755</v>
+        <v>6757451</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13538,7 +13533,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120487900</v>
+        <v>120487895</v>
       </c>
       <c r="B126" t="n">
         <v>78542</v>
@@ -13578,10 +13573,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436417</v>
+        <v>436399</v>
       </c>
       <c r="R126" t="n">
-        <v>6757451</v>
+        <v>6757445</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13640,7 +13635,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120487895</v>
+        <v>120487839</v>
       </c>
       <c r="B127" t="n">
         <v>78542</v>
@@ -13680,10 +13675,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436399</v>
+        <v>436548</v>
       </c>
       <c r="R127" t="n">
-        <v>6757445</v>
+        <v>6757697</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13742,10 +13737,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120487839</v>
+        <v>120487985</v>
       </c>
       <c r="B128" t="n">
-        <v>78542</v>
+        <v>5169</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13754,38 +13749,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436548</v>
+        <v>436401</v>
       </c>
       <c r="R128" t="n">
-        <v>6757697</v>
+        <v>6757463</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13844,10 +13844,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120487979</v>
+        <v>120487757</v>
       </c>
       <c r="B129" t="n">
-        <v>78187</v>
+        <v>57473</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13860,34 +13860,38 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436297</v>
+        <v>436404</v>
       </c>
       <c r="R129" t="n">
-        <v>6757476</v>
+        <v>6757479</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13946,10 +13950,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120487875</v>
+        <v>120487979</v>
       </c>
       <c r="B130" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13962,21 +13966,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13986,10 +13990,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436365</v>
+        <v>436297</v>
       </c>
       <c r="R130" t="n">
-        <v>6757443</v>
+        <v>6757476</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14048,10 +14052,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120487911</v>
+        <v>120487678</v>
       </c>
       <c r="B131" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14064,21 +14068,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14088,10 +14092,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436512</v>
+        <v>436468</v>
       </c>
       <c r="R131" t="n">
-        <v>6757751</v>
+        <v>6757733</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14150,10 +14154,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120487837</v>
+        <v>120487683</v>
       </c>
       <c r="B132" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14166,21 +14170,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14190,10 +14194,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436570</v>
+        <v>436358</v>
       </c>
       <c r="R132" t="n">
-        <v>6757696</v>
+        <v>6757681</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14252,7 +14256,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120487820</v>
+        <v>120487885</v>
       </c>
       <c r="B133" t="n">
         <v>78542</v>
@@ -14292,10 +14296,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>436458</v>
+        <v>436398</v>
       </c>
       <c r="R133" t="n">
-        <v>6757464</v>
+        <v>6757452</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14354,7 +14358,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120487858</v>
+        <v>120487875</v>
       </c>
       <c r="B134" t="n">
         <v>78542</v>
@@ -14394,10 +14398,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436332</v>
+        <v>436365</v>
       </c>
       <c r="R134" t="n">
-        <v>6757673</v>
+        <v>6757443</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14456,10 +14460,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120487757</v>
+        <v>120487911</v>
       </c>
       <c r="B135" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14472,38 +14476,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>436404</v>
+        <v>436512</v>
       </c>
       <c r="R135" t="n">
-        <v>6757479</v>
+        <v>6757751</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14562,10 +14562,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120487678</v>
+        <v>120487837</v>
       </c>
       <c r="B136" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14578,21 +14578,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14602,10 +14602,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>436468</v>
+        <v>436570</v>
       </c>
       <c r="R136" t="n">
-        <v>6757733</v>
+        <v>6757696</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14664,10 +14664,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120487683</v>
+        <v>120487820</v>
       </c>
       <c r="B137" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14680,21 +14680,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>436358</v>
+        <v>436458</v>
       </c>
       <c r="R137" t="n">
-        <v>6757681</v>
+        <v>6757464</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14766,7 +14766,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120487885</v>
+        <v>120487858</v>
       </c>
       <c r="B138" t="n">
         <v>78542</v>
@@ -14806,10 +14806,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>436398</v>
+        <v>436332</v>
       </c>
       <c r="R138" t="n">
-        <v>6757452</v>
+        <v>6757673</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14868,10 +14868,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120487945</v>
+        <v>120487816</v>
       </c>
       <c r="B139" t="n">
-        <v>78187</v>
+        <v>89981</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14880,25 +14880,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>353</v>
+        <v>5685</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14908,10 +14908,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>436480</v>
+        <v>436531</v>
       </c>
       <c r="R139" t="n">
-        <v>6757815</v>
+        <v>6757708</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14970,10 +14970,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120487942</v>
+        <v>120487986</v>
       </c>
       <c r="B140" t="n">
-        <v>78187</v>
+        <v>5169</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14982,38 +14982,43 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>436512</v>
+        <v>436419</v>
       </c>
       <c r="R140" t="n">
-        <v>6757714</v>
+        <v>6757476</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15072,10 +15077,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120487968</v>
+        <v>120487984</v>
       </c>
       <c r="B141" t="n">
-        <v>78187</v>
+        <v>5169</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15084,38 +15089,43 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>436264</v>
+        <v>436366</v>
       </c>
       <c r="R141" t="n">
-        <v>6757686</v>
+        <v>6757441</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15174,10 +15184,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120487709</v>
+        <v>120487808</v>
       </c>
       <c r="B142" t="n">
-        <v>78576</v>
+        <v>8432</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15186,38 +15196,43 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>436480</v>
+        <v>436494</v>
       </c>
       <c r="R142" t="n">
-        <v>6757418</v>
+        <v>6757416</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15276,10 +15291,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120487748</v>
+        <v>120487677</v>
       </c>
       <c r="B143" t="n">
-        <v>90580</v>
+        <v>79160</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15292,43 +15307,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>436425</v>
+        <v>436480</v>
       </c>
       <c r="R143" t="n">
-        <v>6757468</v>
+        <v>6757815</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15489,10 +15495,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120487986</v>
+        <v>120487856</v>
       </c>
       <c r="B145" t="n">
-        <v>5169</v>
+        <v>78542</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15501,43 +15507,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>436419</v>
+        <v>436445</v>
       </c>
       <c r="R145" t="n">
-        <v>6757476</v>
+        <v>6757731</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15596,10 +15597,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120487984</v>
+        <v>120487884</v>
       </c>
       <c r="B146" t="n">
-        <v>5169</v>
+        <v>78542</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15608,43 +15609,38 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436366</v>
+        <v>436390</v>
       </c>
       <c r="R146" t="n">
-        <v>6757441</v>
+        <v>6757447</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15703,10 +15699,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120487808</v>
+        <v>120487838</v>
       </c>
       <c r="B147" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15715,43 +15711,38 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>436494</v>
+        <v>436564</v>
       </c>
       <c r="R147" t="n">
-        <v>6757416</v>
+        <v>6757693</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15810,10 +15801,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120487816</v>
+        <v>120487905</v>
       </c>
       <c r="B148" t="n">
-        <v>89981</v>
+        <v>78542</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15822,25 +15813,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15850,10 +15841,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>436531</v>
+        <v>436468</v>
       </c>
       <c r="R148" t="n">
-        <v>6757708</v>
+        <v>6757429</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15912,10 +15903,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120487677</v>
+        <v>120487759</v>
       </c>
       <c r="B149" t="n">
-        <v>79160</v>
+        <v>57473</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15928,21 +15919,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15952,10 +15943,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436480</v>
+        <v>436419</v>
       </c>
       <c r="R149" t="n">
-        <v>6757815</v>
+        <v>6757476</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16014,10 +16005,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120487856</v>
+        <v>120487748</v>
       </c>
       <c r="B150" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16030,34 +16021,43 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>436445</v>
+        <v>436425</v>
       </c>
       <c r="R150" t="n">
-        <v>6757731</v>
+        <v>6757468</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16116,10 +16116,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120487884</v>
+        <v>120487945</v>
       </c>
       <c r="B151" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16132,21 +16132,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16156,10 +16156,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436390</v>
+        <v>436480</v>
       </c>
       <c r="R151" t="n">
-        <v>6757447</v>
+        <v>6757815</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16218,10 +16218,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120487838</v>
+        <v>120487942</v>
       </c>
       <c r="B152" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16234,21 +16234,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16258,10 +16258,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436564</v>
+        <v>436512</v>
       </c>
       <c r="R152" t="n">
-        <v>6757693</v>
+        <v>6757714</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16320,10 +16320,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120487905</v>
+        <v>120487968</v>
       </c>
       <c r="B153" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16336,21 +16336,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16360,10 +16360,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>436468</v>
+        <v>436264</v>
       </c>
       <c r="R153" t="n">
-        <v>6757429</v>
+        <v>6757686</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16422,10 +16422,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120487759</v>
+        <v>120487709</v>
       </c>
       <c r="B154" t="n">
-        <v>57473</v>
+        <v>78576</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16438,21 +16438,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16462,10 +16462,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>436419</v>
+        <v>436480</v>
       </c>
       <c r="R154" t="n">
-        <v>6757476</v>
+        <v>6757418</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19817,10 +19817,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120487782</v>
+        <v>120487967</v>
       </c>
       <c r="B187" t="n">
-        <v>90864</v>
+        <v>78187</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19833,43 +19833,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>436408</v>
+        <v>436262</v>
       </c>
       <c r="R187" t="n">
-        <v>6757458</v>
+        <v>6757711</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19928,10 +19919,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120487805</v>
+        <v>120487724</v>
       </c>
       <c r="B188" t="n">
-        <v>8432</v>
+        <v>90545</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19944,39 +19935,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>436261</v>
+        <v>436413</v>
       </c>
       <c r="R188" t="n">
-        <v>6757586</v>
+        <v>6757468</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20035,10 +20021,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120487692</v>
+        <v>120487849</v>
       </c>
       <c r="B189" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20051,21 +20037,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20075,10 +20061,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>436268</v>
+        <v>436479</v>
       </c>
       <c r="R189" t="n">
-        <v>6757611</v>
+        <v>6757765</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20137,10 +20123,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>120487696</v>
+        <v>120487782</v>
       </c>
       <c r="B190" t="n">
-        <v>79160</v>
+        <v>90864</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20153,34 +20139,43 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>436297</v>
+        <v>436408</v>
       </c>
       <c r="R190" t="n">
-        <v>6757477</v>
+        <v>6757458</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20239,7 +20234,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>120487687</v>
+        <v>120487692</v>
       </c>
       <c r="B191" t="n">
         <v>79160</v>
@@ -20279,10 +20274,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>436309</v>
+        <v>436268</v>
       </c>
       <c r="R191" t="n">
-        <v>6757626</v>
+        <v>6757611</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20341,10 +20336,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>120487967</v>
+        <v>120487696</v>
       </c>
       <c r="B192" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20357,21 +20352,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20381,10 +20376,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>436262</v>
+        <v>436297</v>
       </c>
       <c r="R192" t="n">
-        <v>6757711</v>
+        <v>6757477</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20443,10 +20438,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>120487724</v>
+        <v>120487687</v>
       </c>
       <c r="B193" t="n">
-        <v>90545</v>
+        <v>79160</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20455,25 +20450,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20483,10 +20478,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>436413</v>
+        <v>436309</v>
       </c>
       <c r="R193" t="n">
-        <v>6757468</v>
+        <v>6757626</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20545,10 +20540,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>120487849</v>
+        <v>120487805</v>
       </c>
       <c r="B194" t="n">
-        <v>78542</v>
+        <v>8432</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20557,38 +20552,43 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>436479</v>
+        <v>436261</v>
       </c>
       <c r="R194" t="n">
-        <v>6757765</v>
+        <v>6757586</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21268,10 +21268,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>120487977</v>
+        <v>120487892</v>
       </c>
       <c r="B201" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21284,21 +21284,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21308,10 +21308,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>436278</v>
+        <v>436424</v>
       </c>
       <c r="R201" t="n">
-        <v>6757591</v>
+        <v>6757469</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21370,10 +21370,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>120487933</v>
+        <v>120487902</v>
       </c>
       <c r="B202" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21386,21 +21386,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21410,10 +21410,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>436528</v>
+        <v>436479</v>
       </c>
       <c r="R202" t="n">
-        <v>6757704</v>
+        <v>6757437</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21472,10 +21472,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>120487774</v>
+        <v>120487893</v>
       </c>
       <c r="B203" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21484,47 +21484,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>436588</v>
+        <v>436412</v>
       </c>
       <c r="R203" t="n">
-        <v>6757482</v>
+        <v>6757470</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21583,10 +21574,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>120487778</v>
+        <v>120487826</v>
       </c>
       <c r="B204" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21599,43 +21590,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>436453</v>
+        <v>436585</v>
       </c>
       <c r="R204" t="n">
-        <v>6757734</v>
+        <v>6757484</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21694,10 +21676,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>120487892</v>
+        <v>120487977</v>
       </c>
       <c r="B205" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21710,21 +21692,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21734,10 +21716,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>436424</v>
+        <v>436278</v>
       </c>
       <c r="R205" t="n">
-        <v>6757469</v>
+        <v>6757591</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21796,10 +21778,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>120487902</v>
+        <v>120487933</v>
       </c>
       <c r="B206" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21812,21 +21794,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21836,10 +21818,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>436479</v>
+        <v>436528</v>
       </c>
       <c r="R206" t="n">
-        <v>6757437</v>
+        <v>6757704</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21898,10 +21880,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>120487893</v>
+        <v>120487778</v>
       </c>
       <c r="B207" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21914,34 +21896,43 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>436412</v>
+        <v>436453</v>
       </c>
       <c r="R207" t="n">
-        <v>6757470</v>
+        <v>6757734</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22000,10 +21991,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>120487826</v>
+        <v>120487774</v>
       </c>
       <c r="B208" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22012,38 +22003,47 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>436585</v>
+        <v>436588</v>
       </c>
       <c r="R208" t="n">
-        <v>6757484</v>
+        <v>6757482</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>

--- a/artfynd/A 5140-2024 artfynd.xlsx
+++ b/artfynd/A 5140-2024 artfynd.xlsx
@@ -22105,7 +22105,7 @@
         <v>120487768</v>
       </c>
       <c r="B209" t="n">
-        <v>57348</v>
+        <v>57478</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>120487752</v>
       </c>
       <c r="B210" t="n">
-        <v>57348</v>
+        <v>57478</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>120487751</v>
       </c>
       <c r="B211" t="n">
-        <v>57348</v>
+        <v>57478</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>

--- a/artfynd/A 5140-2024 artfynd.xlsx
+++ b/artfynd/A 5140-2024 artfynd.xlsx
@@ -22105,7 +22105,7 @@
         <v>120487768</v>
       </c>
       <c r="B209" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>120487752</v>
       </c>
       <c r="B210" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>120487751</v>
       </c>
       <c r="B211" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
